--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -684,7 +684,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.714.387-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.185.932-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>96.827.350-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.734.221-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1063,7 +1083,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>584105-291-CM25</t>
+          <t>730566-248-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,12 +1108,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,28 +1123,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>19038.46</v>
+        <v>44731.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2735-795-CM25</t>
+          <t>584105-291-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1173,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1188,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1203,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>20051.11</v>
+        <v>19038.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>730566-248-CM25</t>
+          <t>2735-795-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1234,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1249,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1264,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>44731.6</v>
+        <v>20051.11</v>
       </c>
     </row>
     <row r="14">
@@ -1355,7 +1379,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1444,11 @@
           <t>77.363.384-3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>96.771.610-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1635,11 @@
           <t>76.504.980-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1673,7 +1713,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1602-74-CM25</t>
+          <t>1314-89-CM24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1733,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,28 +1753,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>VAB Ingeniería de Software Limitada</t>
+          <t>SOLUCIONES INFORMATICAS GLOBAL SYSTEM LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.090.261-6</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.220.478-9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>11071.25</v>
+        <v>26633.93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1314-89-CM24</t>
+          <t>2291-852-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,32 +1798,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SOLUCIONES INFORMATICAS GLOBAL SYSTEM LIMITADA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.220.478-9</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1833,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>26633.93</v>
+        <v>45683.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2291-852-CM25</t>
+          <t>1602-74-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,27 +1864,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>VAB Ingeniería de Software Limitada</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.090.261-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1894,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>45683.89</v>
+        <v>11071.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4201-411-CM25</t>
+          <t>1588-128-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,27 +1925,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>76.444.489-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1955,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41343.66</v>
+        <v>32097.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1005498-146-CM25</t>
+          <t>4201-411-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,12 +1986,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,28 +2001,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.561.404-k</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>48104.81</v>
+        <v>41343.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1588-128-CM25</t>
+          <t>1005498-146-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,27 +2051,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
+          <t>76.561.404-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2081,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>32097.8</v>
+        <v>48104.81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1588-143-CM25</t>
+          <t>3553-290-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2112,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,28 +2127,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ACS INGENIEROS SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.240.927-5</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>18312.05</v>
+        <v>8651.76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3553-290-CM25</t>
+          <t>1588-143-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,12 +2177,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2192,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>ACS INGENIEROS SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.240.927-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,7 +2207,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8651.76</v>
+        <v>18312.05</v>
       </c>
     </row>
     <row r="29">
@@ -2270,7 +2322,11 @@
           <t>96.986.170-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2448,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2405,7 +2465,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1019-284-CM25</t>
+          <t>1876-92-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2425,17 +2485,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2505,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INFORMATICA Y SISTEMAS COMPUTACIONALES ORBIS LIMITADA</t>
+          <t>NETICS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.758.914-8</t>
+          <t>76.363.873-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2520,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7368.11</v>
+        <v>67200.92999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1876-92-CM25</t>
+          <t>1609-203-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,43 +2551,47 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NETICS SPA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.363.873-1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>67200.92999999999</v>
+        <v>30259.78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1609-203-CM25</t>
+          <t>721703-281-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,27 +2616,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.980.230-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.213.064-5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2646,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>30259.78</v>
+        <v>13190.77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>721703-281-CM25</t>
+          <t>1019-284-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,17 +2672,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.980.230-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,22 +2692,26 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+          <t>INFORMATICA Y SISTEMAS COMPUTACIONALES ORBIS LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.213.064-5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.758.914-8</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>13190.77</v>
+        <v>7368.11</v>
       </c>
     </row>
     <row r="37">
@@ -2697,7 +2765,11 @@
           <t>76.734.221-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2710,7 +2782,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1602-77-CM25</t>
+          <t>587-167-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,12 +2807,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,28 +2822,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>19271.49</v>
+        <v>834321.6800000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>587-167-CM25</t>
+          <t>1602-77-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,12 +2872,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,22 +2887,26 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>834321.6800000001</v>
+        <v>19271.49</v>
       </c>
     </row>
     <row r="40">
@@ -2880,7 +2960,11 @@
           <t>96.771.610-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3025,11 @@
           <t>96.771.610-3</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3151,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3277,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3259,7 +3355,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1725-5031-CM25</t>
+          <t>33-1-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3279,32 +3375,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.444.489-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3410,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>19605.28</v>
+        <v>41913.86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1469-1704-CM25</t>
+          <t>33-2-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,27 +3441,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOCIEDAD LIGARIUS SPA</t>
+          <t>CONSULTORIA Y SISTEMAS DE INFORMACION LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.063.547-0</t>
+          <t>76.291.521-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3471,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>41437.18</v>
+        <v>16002.31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>33-1-CM25</t>
+          <t>1725-5031-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,48 +3497,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>41913.86</v>
+        <v>19605.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>33-2-CM25</t>
+          <t>1469-1704-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3467,27 +3567,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y SISTEMAS DE INFORMACION LIMITADA</t>
+          <t>SOCIEDAD LIGARIUS SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.291.521-9</t>
+          <t>77.063.547-0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,7 +3597,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>16002.31</v>
+        <v>41437.18</v>
       </c>
     </row>
     <row r="51">
@@ -3551,7 +3651,11 @@
           <t>77.842.230-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3559,6 +3663,71 @@
       </c>
       <c r="M51" s="2" t="n">
         <v>108664.33</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1057547-24798-SE25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>47226.81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2025.xlsx
@@ -3342,7 +3342,11 @@
           <t>76.164.712-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
